--- a/backend/app/db/seed/data/conversion.xlsx
+++ b/backend/app/db/seed/data/conversion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SupplyChain- mobile\backend\app\db\seed\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8795E0EC-9DC2-4482-966D-C3AE1DE7598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E71BE15-7E4E-4C2C-B5A9-BE1FAA84BFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="116">
   <si>
     <t xml:space="preserve">APPLE AMBRI </t>
   </si>
@@ -346,6 +346,33 @@
   </si>
   <si>
     <t>factor</t>
+  </si>
+  <si>
+    <t>BEL PATTA</t>
+  </si>
+  <si>
+    <t>BETEL LEAVES</t>
+  </si>
+  <si>
+    <t>BROCCOLI</t>
+  </si>
+  <si>
+    <t>MANGO CHAUNSA</t>
+  </si>
+  <si>
+    <t>DRAGON FRUIT (RED FLESH)</t>
+  </si>
+  <si>
+    <t>RADISH</t>
+  </si>
+  <si>
+    <t>GROUNDNUT</t>
+  </si>
+  <si>
+    <t>TULSI</t>
+  </si>
+  <si>
+    <t>SPINE GOURD</t>
   </si>
 </sst>
 </file>
@@ -663,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.19921875" bestFit="1" customWidth="1"/>
@@ -2100,6 +2127,132 @@
         <v>1</v>
       </c>
     </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>108</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>109</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>110</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>111</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>112</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>113</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
